--- a/fil-c-x64/Running insertion.xlsx
+++ b/fil-c-x64/Running insertion.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>55.2328</v>
+        <v>55.1739</v>
       </c>
       <c r="C2" t="n">
-        <v>82.6602</v>
+        <v>82.6276</v>
       </c>
       <c r="D2" t="n">
-        <v>130.496</v>
+        <v>129.683</v>
       </c>
       <c r="E2" t="n">
-        <v>55.686</v>
+        <v>55.6129</v>
       </c>
       <c r="F2" t="n">
-        <v>78.1617</v>
+        <v>78.2671</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>53.9874</v>
+        <v>53.9366</v>
       </c>
       <c r="C3" t="n">
-        <v>81.239</v>
+        <v>81.0061</v>
       </c>
       <c r="D3" t="n">
-        <v>129.359</v>
+        <v>128.986</v>
       </c>
       <c r="E3" t="n">
-        <v>53.952</v>
+        <v>54.0445</v>
       </c>
       <c r="F3" t="n">
-        <v>76.809</v>
+        <v>76.658</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>52.726</v>
+        <v>52.6908</v>
       </c>
       <c r="C4" t="n">
-        <v>79.1452</v>
+        <v>79.3554</v>
       </c>
       <c r="D4" t="n">
-        <v>126.714</v>
+        <v>126.118</v>
       </c>
       <c r="E4" t="n">
-        <v>52.5822</v>
+        <v>52.6039</v>
       </c>
       <c r="F4" t="n">
-        <v>74.8133</v>
+        <v>74.88979999999999</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>51.4458</v>
+        <v>51.4596</v>
       </c>
       <c r="C5" t="n">
-        <v>77.4756</v>
+        <v>77.4635</v>
       </c>
       <c r="D5" t="n">
-        <v>124.614</v>
+        <v>124.432</v>
       </c>
       <c r="E5" t="n">
-        <v>51.3794</v>
+        <v>51.448</v>
       </c>
       <c r="F5" t="n">
-        <v>73.8064</v>
+        <v>73.4588</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>50.2337</v>
+        <v>50.2394</v>
       </c>
       <c r="C6" t="n">
-        <v>75.7337</v>
+        <v>75.7102</v>
       </c>
       <c r="D6" t="n">
-        <v>123.224</v>
+        <v>122.263</v>
       </c>
       <c r="E6" t="n">
-        <v>50.3318</v>
+        <v>50.397</v>
       </c>
       <c r="F6" t="n">
-        <v>72.1788</v>
+        <v>71.9893</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>49.4058</v>
+        <v>49.3912</v>
       </c>
       <c r="C7" t="n">
-        <v>74.92700000000001</v>
+        <v>74.5262</v>
       </c>
       <c r="D7" t="n">
-        <v>170.654</v>
+        <v>169.311</v>
       </c>
       <c r="E7" t="n">
-        <v>49.4335</v>
+        <v>49.4154</v>
       </c>
       <c r="F7" t="n">
-        <v>71.0074</v>
+        <v>70.71299999999999</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>48.5986</v>
+        <v>48.5644</v>
       </c>
       <c r="C8" t="n">
-        <v>73.4558</v>
+        <v>73.33580000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>167.958</v>
+        <v>167.386</v>
       </c>
       <c r="E8" t="n">
-        <v>48.8038</v>
+        <v>48.8456</v>
       </c>
       <c r="F8" t="n">
-        <v>69.8989</v>
+        <v>69.9744</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>47.9651</v>
+        <v>47.9351</v>
       </c>
       <c r="C9" t="n">
-        <v>72.6005</v>
+        <v>72.7139</v>
       </c>
       <c r="D9" t="n">
-        <v>162.526</v>
+        <v>162.952</v>
       </c>
       <c r="E9" t="n">
-        <v>68.1212</v>
+        <v>68.1086</v>
       </c>
       <c r="F9" t="n">
-        <v>100.206</v>
+        <v>98.7128</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>64.9058</v>
+        <v>64.9605</v>
       </c>
       <c r="C10" t="n">
-        <v>104.669</v>
+        <v>103.68</v>
       </c>
       <c r="D10" t="n">
-        <v>159.898</v>
+        <v>158.465</v>
       </c>
       <c r="E10" t="n">
-        <v>65.97920000000001</v>
+        <v>66.078</v>
       </c>
       <c r="F10" t="n">
-        <v>97.8549</v>
+        <v>96.29130000000001</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>63.0563</v>
+        <v>63.2066</v>
       </c>
       <c r="C11" t="n">
-        <v>101.381</v>
+        <v>100.746</v>
       </c>
       <c r="D11" t="n">
-        <v>154.949</v>
+        <v>154.077</v>
       </c>
       <c r="E11" t="n">
-        <v>63.9303</v>
+        <v>64.0842</v>
       </c>
       <c r="F11" t="n">
-        <v>94.1096</v>
+        <v>93.6157</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>61.3648</v>
+        <v>61.5072</v>
       </c>
       <c r="C12" t="n">
-        <v>98.35639999999999</v>
+        <v>98.0977</v>
       </c>
       <c r="D12" t="n">
-        <v>153.26</v>
+        <v>152.153</v>
       </c>
       <c r="E12" t="n">
-        <v>62.0944</v>
+        <v>62.1815</v>
       </c>
       <c r="F12" t="n">
-        <v>91.9734</v>
+        <v>91.28489999999999</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>59.8143</v>
+        <v>59.9109</v>
       </c>
       <c r="C13" t="n">
-        <v>96.1023</v>
+        <v>95.60760000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>149.345</v>
+        <v>148.809</v>
       </c>
       <c r="E13" t="n">
-        <v>60.3647</v>
+        <v>60.3981</v>
       </c>
       <c r="F13" t="n">
-        <v>89.51860000000001</v>
+        <v>89.3342</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>58.2646</v>
+        <v>58.2502</v>
       </c>
       <c r="C14" t="n">
-        <v>93.3296</v>
+        <v>93.46729999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>146.906</v>
+        <v>146.85</v>
       </c>
       <c r="E14" t="n">
-        <v>58.5835</v>
+        <v>58.7259</v>
       </c>
       <c r="F14" t="n">
-        <v>87.1934</v>
+        <v>87.2086</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>56.6619</v>
+        <v>56.8903</v>
       </c>
       <c r="C15" t="n">
-        <v>91.77500000000001</v>
+        <v>91.7812</v>
       </c>
       <c r="D15" t="n">
-        <v>144.141</v>
+        <v>144.262</v>
       </c>
       <c r="E15" t="n">
-        <v>57.0208</v>
+        <v>57.1348</v>
       </c>
       <c r="F15" t="n">
-        <v>84.87009999999999</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>55.3385</v>
+        <v>55.4674</v>
       </c>
       <c r="C16" t="n">
-        <v>89.3068</v>
+        <v>89.68810000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>141.868</v>
+        <v>141.533</v>
       </c>
       <c r="E16" t="n">
-        <v>55.5789</v>
+        <v>55.624</v>
       </c>
       <c r="F16" t="n">
-        <v>82.5896</v>
+        <v>82.3869</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>54.0565</v>
+        <v>54.0514</v>
       </c>
       <c r="C17" t="n">
-        <v>86.8934</v>
+        <v>86.4594</v>
       </c>
       <c r="D17" t="n">
-        <v>139.225</v>
+        <v>139.039</v>
       </c>
       <c r="E17" t="n">
-        <v>54.1698</v>
+        <v>54.2504</v>
       </c>
       <c r="F17" t="n">
-        <v>81.1579</v>
+        <v>80.35599999999999</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>52.837</v>
+        <v>52.9266</v>
       </c>
       <c r="C18" t="n">
-        <v>85.17570000000001</v>
+        <v>84.52119999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>136.259</v>
+        <v>137.31</v>
       </c>
       <c r="E18" t="n">
-        <v>52.906</v>
+        <v>52.9102</v>
       </c>
       <c r="F18" t="n">
-        <v>79.7714</v>
+        <v>78.7251</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>51.7148</v>
+        <v>51.782</v>
       </c>
       <c r="C19" t="n">
-        <v>82.5823</v>
+        <v>82.41330000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>136.099</v>
+        <v>135.577</v>
       </c>
       <c r="E19" t="n">
-        <v>51.5953</v>
+        <v>51.7072</v>
       </c>
       <c r="F19" t="n">
-        <v>77.3276</v>
+        <v>76.9055</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>50.6453</v>
+        <v>50.7236</v>
       </c>
       <c r="C20" t="n">
-        <v>81.04040000000001</v>
+        <v>80.754</v>
       </c>
       <c r="D20" t="n">
-        <v>133.886</v>
+        <v>133.988</v>
       </c>
       <c r="E20" t="n">
-        <v>50.5828</v>
+        <v>50.5763</v>
       </c>
       <c r="F20" t="n">
-        <v>75.4021</v>
+        <v>75.7907</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>49.7695</v>
+        <v>49.7551</v>
       </c>
       <c r="C21" t="n">
-        <v>79.3425</v>
+        <v>79.242</v>
       </c>
       <c r="D21" t="n">
-        <v>185.836</v>
+        <v>186.033</v>
       </c>
       <c r="E21" t="n">
-        <v>49.665</v>
+        <v>49.7388</v>
       </c>
       <c r="F21" t="n">
-        <v>74.0822</v>
+        <v>75.1071</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>48.9944</v>
+        <v>49.0665</v>
       </c>
       <c r="C22" t="n">
-        <v>78.087</v>
+        <v>79.04049999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>181.632</v>
+        <v>183.482</v>
       </c>
       <c r="E22" t="n">
-        <v>49.0211</v>
+        <v>49.0568</v>
       </c>
       <c r="F22" t="n">
-        <v>73.0806</v>
+        <v>73.6758</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>48.4681</v>
+        <v>48.5614</v>
       </c>
       <c r="C23" t="n">
-        <v>77.03270000000001</v>
+        <v>77.3903</v>
       </c>
       <c r="D23" t="n">
-        <v>176.727</v>
+        <v>177.08</v>
       </c>
       <c r="E23" t="n">
-        <v>68.8959</v>
+        <v>69.3383</v>
       </c>
       <c r="F23" t="n">
-        <v>106.316</v>
+        <v>105.509</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>65.991</v>
+        <v>66.2548</v>
       </c>
       <c r="C24" t="n">
-        <v>111.454</v>
+        <v>111.06</v>
       </c>
       <c r="D24" t="n">
-        <v>173.632</v>
+        <v>171.479</v>
       </c>
       <c r="E24" t="n">
-        <v>66.8249</v>
+        <v>66.892</v>
       </c>
       <c r="F24" t="n">
-        <v>102.661</v>
+        <v>101.38</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>64.2831</v>
+        <v>64.3638</v>
       </c>
       <c r="C25" t="n">
-        <v>108.249</v>
+        <v>108.077</v>
       </c>
       <c r="D25" t="n">
-        <v>169.224</v>
+        <v>168.052</v>
       </c>
       <c r="E25" t="n">
-        <v>64.8425</v>
+        <v>65.02889999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>99.9328</v>
+        <v>100.535</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>62.6652</v>
+        <v>62.803</v>
       </c>
       <c r="C26" t="n">
-        <v>105.962</v>
+        <v>105.988</v>
       </c>
       <c r="D26" t="n">
-        <v>166.692</v>
+        <v>165.506</v>
       </c>
       <c r="E26" t="n">
-        <v>63.0518</v>
+        <v>63.1185</v>
       </c>
       <c r="F26" t="n">
-        <v>96.6708</v>
+        <v>97.07769999999999</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>61.0321</v>
+        <v>61.1462</v>
       </c>
       <c r="C27" t="n">
-        <v>102.459</v>
+        <v>102.399</v>
       </c>
       <c r="D27" t="n">
-        <v>162.846</v>
+        <v>162.868</v>
       </c>
       <c r="E27" t="n">
-        <v>61.3019</v>
+        <v>61.4026</v>
       </c>
       <c r="F27" t="n">
-        <v>95.29600000000001</v>
+        <v>96.1331</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>59.6245</v>
+        <v>59.6421</v>
       </c>
       <c r="C28" t="n">
-        <v>100.043</v>
+        <v>99.5577</v>
       </c>
       <c r="D28" t="n">
-        <v>159.358</v>
+        <v>158.49</v>
       </c>
       <c r="E28" t="n">
-        <v>59.6002</v>
+        <v>59.6119</v>
       </c>
       <c r="F28" t="n">
-        <v>92.02760000000001</v>
+        <v>92.0253</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>58.0653</v>
+        <v>58.1083</v>
       </c>
       <c r="C29" t="n">
-        <v>97.3201</v>
+        <v>97.2354</v>
       </c>
       <c r="D29" t="n">
-        <v>157.348</v>
+        <v>157.207</v>
       </c>
       <c r="E29" t="n">
-        <v>57.9727</v>
+        <v>58.0945</v>
       </c>
       <c r="F29" t="n">
-        <v>89.6177</v>
+        <v>90.00660000000001</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>57.2509</v>
+        <v>56.7959</v>
       </c>
       <c r="C30" t="n">
-        <v>95.7517</v>
+        <v>95.6143</v>
       </c>
       <c r="D30" t="n">
-        <v>154.223</v>
+        <v>153.607</v>
       </c>
       <c r="E30" t="n">
-        <v>56.5918</v>
+        <v>56.5814</v>
       </c>
       <c r="F30" t="n">
-        <v>86.4961</v>
+        <v>86.5665</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>55.4095</v>
+        <v>55.4094</v>
       </c>
       <c r="C31" t="n">
-        <v>93.4791</v>
+        <v>93.32980000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>153.33</v>
+        <v>152.418</v>
       </c>
       <c r="E31" t="n">
-        <v>55.0724</v>
+        <v>55.1347</v>
       </c>
       <c r="F31" t="n">
-        <v>86.76139999999999</v>
+        <v>86.7948</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>54.1309</v>
+        <v>54.1449</v>
       </c>
       <c r="C32" t="n">
-        <v>91.1862</v>
+        <v>91.0699</v>
       </c>
       <c r="D32" t="n">
-        <v>149.565</v>
+        <v>148.851</v>
       </c>
       <c r="E32" t="n">
-        <v>53.8079</v>
+        <v>53.8145</v>
       </c>
       <c r="F32" t="n">
-        <v>83.2529</v>
+        <v>83.4228</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>53.0812</v>
+        <v>53.0131</v>
       </c>
       <c r="C33" t="n">
-        <v>88.6767</v>
+        <v>87.9615</v>
       </c>
       <c r="D33" t="n">
-        <v>146.407</v>
+        <v>146.402</v>
       </c>
       <c r="E33" t="n">
-        <v>52.6492</v>
+        <v>52.6112</v>
       </c>
       <c r="F33" t="n">
-        <v>82.43470000000001</v>
+        <v>82.3763</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>51.9687</v>
+        <v>51.9526</v>
       </c>
       <c r="C34" t="n">
-        <v>87.26990000000001</v>
+        <v>87.0728</v>
       </c>
       <c r="D34" t="n">
-        <v>146.761</v>
+        <v>145.692</v>
       </c>
       <c r="E34" t="n">
-        <v>51.5074</v>
+        <v>51.5446</v>
       </c>
       <c r="F34" t="n">
-        <v>79.73779999999999</v>
+        <v>79.2617</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>50.9017</v>
+        <v>51.1411</v>
       </c>
       <c r="C35" t="n">
-        <v>85.1855</v>
+        <v>84.70699999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>205.077</v>
+        <v>203.1</v>
       </c>
       <c r="E35" t="n">
-        <v>50.5783</v>
+        <v>50.6544</v>
       </c>
       <c r="F35" t="n">
-        <v>79.6711</v>
+        <v>79.3233</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>50.2048</v>
+        <v>50.2242</v>
       </c>
       <c r="C36" t="n">
-        <v>84.2253</v>
+        <v>83.92440000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>203.833</v>
+        <v>199.561</v>
       </c>
       <c r="E36" t="n">
-        <v>49.8716</v>
+        <v>49.9488</v>
       </c>
       <c r="F36" t="n">
-        <v>77.0035</v>
+        <v>77.4258</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>49.4777</v>
+        <v>49.5875</v>
       </c>
       <c r="C37" t="n">
-        <v>82.0415</v>
+        <v>81.7517</v>
       </c>
       <c r="D37" t="n">
-        <v>195.938</v>
+        <v>194.026</v>
       </c>
       <c r="E37" t="n">
-        <v>70.4659</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>114.035</v>
+        <v>114.461</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>67.9825</v>
+        <v>67.9534</v>
       </c>
       <c r="C38" t="n">
-        <v>119.946</v>
+        <v>122.402</v>
       </c>
       <c r="D38" t="n">
-        <v>189.955</v>
+        <v>192.089</v>
       </c>
       <c r="E38" t="n">
-        <v>68.42959999999999</v>
+        <v>68.48260000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>108.941</v>
+        <v>108.419</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>66.151</v>
+        <v>66.274</v>
       </c>
       <c r="C39" t="n">
-        <v>118.662</v>
+        <v>118.992</v>
       </c>
       <c r="D39" t="n">
-        <v>185.877</v>
+        <v>185.672</v>
       </c>
       <c r="E39" t="n">
-        <v>66.4278</v>
+        <v>66.41889999999999</v>
       </c>
       <c r="F39" t="n">
-        <v>107.17</v>
+        <v>106.204</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>64.49469999999999</v>
+        <v>64.509</v>
       </c>
       <c r="C40" t="n">
-        <v>113.684</v>
+        <v>112.481</v>
       </c>
       <c r="D40" t="n">
-        <v>183.4</v>
+        <v>181.569</v>
       </c>
       <c r="E40" t="n">
-        <v>64.491</v>
+        <v>64.5877</v>
       </c>
       <c r="F40" t="n">
-        <v>106.078</v>
+        <v>102.201</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>62.8333</v>
+        <v>62.9101</v>
       </c>
       <c r="C41" t="n">
-        <v>111.611</v>
+        <v>110.06</v>
       </c>
       <c r="D41" t="n">
-        <v>181.877</v>
+        <v>177.941</v>
       </c>
       <c r="E41" t="n">
-        <v>62.6402</v>
+        <v>62.7635</v>
       </c>
       <c r="F41" t="n">
-        <v>103.211</v>
+        <v>100.357</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>61.0416</v>
+        <v>61.1842</v>
       </c>
       <c r="C42" t="n">
-        <v>109.268</v>
+        <v>107.862</v>
       </c>
       <c r="D42" t="n">
-        <v>173.646</v>
+        <v>174.195</v>
       </c>
       <c r="E42" t="n">
-        <v>60.94</v>
+        <v>61.1683</v>
       </c>
       <c r="F42" t="n">
-        <v>98.8265</v>
+        <v>97.16</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>59.6251</v>
+        <v>59.8441</v>
       </c>
       <c r="C43" t="n">
-        <v>105.631</v>
+        <v>104.908</v>
       </c>
       <c r="D43" t="n">
-        <v>170.44</v>
+        <v>170.505</v>
       </c>
       <c r="E43" t="n">
-        <v>59.2901</v>
+        <v>59.4931</v>
       </c>
       <c r="F43" t="n">
-        <v>98.1277</v>
+        <v>97.07559999999999</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>58.204</v>
+        <v>58.4273</v>
       </c>
       <c r="C44" t="n">
-        <v>102.408</v>
+        <v>103.38</v>
       </c>
       <c r="D44" t="n">
-        <v>166.085</v>
+        <v>168.68</v>
       </c>
       <c r="E44" t="n">
-        <v>57.7249</v>
+        <v>57.9046</v>
       </c>
       <c r="F44" t="n">
-        <v>94.7166</v>
+        <v>94.34139999999999</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>56.8477</v>
+        <v>57.0444</v>
       </c>
       <c r="C45" t="n">
-        <v>101.319</v>
+        <v>100.847</v>
       </c>
       <c r="D45" t="n">
-        <v>166.771</v>
+        <v>167.61</v>
       </c>
       <c r="E45" t="n">
-        <v>56.2827</v>
+        <v>56.4623</v>
       </c>
       <c r="F45" t="n">
-        <v>91.77379999999999</v>
+        <v>92.0714</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>55.6338</v>
+        <v>55.7803</v>
       </c>
       <c r="C46" t="n">
-        <v>99.4345</v>
+        <v>99.6508</v>
       </c>
       <c r="D46" t="n">
-        <v>163.225</v>
+        <v>164.379</v>
       </c>
       <c r="E46" t="n">
-        <v>55.0734</v>
+        <v>55.1142</v>
       </c>
       <c r="F46" t="n">
-        <v>88.2647</v>
+        <v>88.18980000000001</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>54.5439</v>
+        <v>54.5195</v>
       </c>
       <c r="C47" t="n">
-        <v>96.929</v>
+        <v>97.053</v>
       </c>
       <c r="D47" t="n">
-        <v>163.925</v>
+        <v>161.538</v>
       </c>
       <c r="E47" t="n">
-        <v>53.7593</v>
+        <v>53.8591</v>
       </c>
       <c r="F47" t="n">
-        <v>89.3014</v>
+        <v>86.43089999999999</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>53.3845</v>
+        <v>53.5118</v>
       </c>
       <c r="C48" t="n">
-        <v>94.7016</v>
+        <v>93.6484</v>
       </c>
       <c r="D48" t="n">
-        <v>159.361</v>
+        <v>155.828</v>
       </c>
       <c r="E48" t="n">
-        <v>52.705</v>
+        <v>52.7653</v>
       </c>
       <c r="F48" t="n">
-        <v>86.73699999999999</v>
+        <v>84.7411</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>52.4305</v>
+        <v>52.5564</v>
       </c>
       <c r="C49" t="n">
-        <v>93.02800000000001</v>
+        <v>92.20359999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>156.089</v>
+        <v>155.134</v>
       </c>
       <c r="E49" t="n">
-        <v>51.8222</v>
+        <v>51.9009</v>
       </c>
       <c r="F49" t="n">
-        <v>83.6238</v>
+        <v>85.28279999999999</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>51.6752</v>
+        <v>51.6832</v>
       </c>
       <c r="C50" t="n">
-        <v>89.76439999999999</v>
+        <v>91.5338</v>
       </c>
       <c r="D50" t="n">
-        <v>236.438</v>
+        <v>239.018</v>
       </c>
       <c r="E50" t="n">
-        <v>51.058</v>
+        <v>51.1376</v>
       </c>
       <c r="F50" t="n">
-        <v>83.1666</v>
+        <v>84.232</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>50.9318</v>
+        <v>50.966</v>
       </c>
       <c r="C51" t="n">
-        <v>89.10429999999999</v>
+        <v>89.4096</v>
       </c>
       <c r="D51" t="n">
-        <v>233.239</v>
+        <v>233.324</v>
       </c>
       <c r="E51" t="n">
-        <v>72.5198</v>
+        <v>72.72620000000001</v>
       </c>
       <c r="F51" t="n">
-        <v>129.345</v>
+        <v>129.802</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>50.5684</v>
+        <v>50.5979</v>
       </c>
       <c r="C52" t="n">
-        <v>89.1752</v>
+        <v>89.86750000000001</v>
       </c>
       <c r="D52" t="n">
-        <v>227.456</v>
+        <v>229.825</v>
       </c>
       <c r="E52" t="n">
-        <v>70.44</v>
+        <v>70.7193</v>
       </c>
       <c r="F52" t="n">
-        <v>124.258</v>
+        <v>118.807</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>68.0279</v>
+        <v>68.47669999999999</v>
       </c>
       <c r="C53" t="n">
-        <v>133.074</v>
+        <v>131.436</v>
       </c>
       <c r="D53" t="n">
-        <v>220.214</v>
+        <v>222.162</v>
       </c>
       <c r="E53" t="n">
-        <v>68.4978</v>
+        <v>68.4649</v>
       </c>
       <c r="F53" t="n">
-        <v>121.543</v>
+        <v>121.373</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>66.2702</v>
+        <v>66.5646</v>
       </c>
       <c r="C54" t="n">
-        <v>127.206</v>
+        <v>127.266</v>
       </c>
       <c r="D54" t="n">
-        <v>214.585</v>
+        <v>216.07</v>
       </c>
       <c r="E54" t="n">
-        <v>66.6465</v>
+        <v>66.5455</v>
       </c>
       <c r="F54" t="n">
-        <v>115.558</v>
+        <v>115.735</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>64.58629999999999</v>
+        <v>64.8801</v>
       </c>
       <c r="C55" t="n">
-        <v>125.038</v>
+        <v>125.819</v>
       </c>
       <c r="D55" t="n">
-        <v>206.282</v>
+        <v>211.234</v>
       </c>
       <c r="E55" t="n">
-        <v>64.8241</v>
+        <v>64.6486</v>
       </c>
       <c r="F55" t="n">
-        <v>111.756</v>
+        <v>111.51</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>62.9627</v>
+        <v>63.1082</v>
       </c>
       <c r="C56" t="n">
-        <v>121.996</v>
+        <v>121.357</v>
       </c>
       <c r="D56" t="n">
-        <v>205.997</v>
+        <v>206.357</v>
       </c>
       <c r="E56" t="n">
-        <v>63.1119</v>
+        <v>63.0415</v>
       </c>
       <c r="F56" t="n">
-        <v>108.724</v>
+        <v>108.673</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>61.4763</v>
+        <v>61.7232</v>
       </c>
       <c r="C57" t="n">
-        <v>120.366</v>
+        <v>119.462</v>
       </c>
       <c r="D57" t="n">
-        <v>209.114</v>
+        <v>207.382</v>
       </c>
       <c r="E57" t="n">
-        <v>61.5404</v>
+        <v>61.5344</v>
       </c>
       <c r="F57" t="n">
-        <v>104.789</v>
+        <v>102.628</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>60.0829</v>
+        <v>60.2876</v>
       </c>
       <c r="C58" t="n">
-        <v>117.714</v>
+        <v>113.213</v>
       </c>
       <c r="D58" t="n">
-        <v>201.09</v>
+        <v>203.884</v>
       </c>
       <c r="E58" t="n">
-        <v>59.9816</v>
+        <v>60.0541</v>
       </c>
       <c r="F58" t="n">
-        <v>98.94970000000001</v>
+        <v>102.445</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>58.782</v>
+        <v>58.8869</v>
       </c>
       <c r="C59" t="n">
-        <v>113.426</v>
+        <v>114.779</v>
       </c>
       <c r="D59" t="n">
-        <v>200.063</v>
+        <v>197.011</v>
       </c>
       <c r="E59" t="n">
-        <v>58.487</v>
+        <v>58.4425</v>
       </c>
       <c r="F59" t="n">
-        <v>97.4131</v>
+        <v>99.8104</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>57.5904</v>
+        <v>57.5335</v>
       </c>
       <c r="C60" t="n">
-        <v>110.074</v>
+        <v>111.193</v>
       </c>
       <c r="D60" t="n">
-        <v>199.705</v>
+        <v>205.424</v>
       </c>
       <c r="E60" t="n">
-        <v>57.1301</v>
+        <v>57.236</v>
       </c>
       <c r="F60" t="n">
-        <v>100.575</v>
+        <v>101.171</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>56.3742</v>
+        <v>56.4738</v>
       </c>
       <c r="C61" t="n">
-        <v>107.782</v>
+        <v>107.901</v>
       </c>
       <c r="D61" t="n">
-        <v>195.745</v>
+        <v>195.693</v>
       </c>
       <c r="E61" t="n">
-        <v>55.9705</v>
+        <v>56.0846</v>
       </c>
       <c r="F61" t="n">
-        <v>98.1661</v>
+        <v>98.5544</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>55.2818</v>
+        <v>55.2589</v>
       </c>
       <c r="C62" t="n">
-        <v>105.037</v>
+        <v>106.306</v>
       </c>
       <c r="D62" t="n">
-        <v>196.097</v>
+        <v>197.487</v>
       </c>
       <c r="E62" t="n">
-        <v>54.7732</v>
+        <v>54.7988</v>
       </c>
       <c r="F62" t="n">
-        <v>92.96169999999999</v>
+        <v>93.498</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>54.2319</v>
+        <v>54.2745</v>
       </c>
       <c r="C63" t="n">
-        <v>100.953</v>
+        <v>104.077</v>
       </c>
       <c r="D63" t="n">
-        <v>191.235</v>
+        <v>194.274</v>
       </c>
       <c r="E63" t="n">
-        <v>53.9405</v>
+        <v>53.6968</v>
       </c>
       <c r="F63" t="n">
-        <v>90.73050000000001</v>
+        <v>91.313</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>53.3852</v>
+        <v>53.4745</v>
       </c>
       <c r="C64" t="n">
-        <v>101.358</v>
+        <v>101.318</v>
       </c>
       <c r="D64" t="n">
-        <v>385.938</v>
+        <v>385.651</v>
       </c>
       <c r="E64" t="n">
-        <v>52.8022</v>
+        <v>52.9816</v>
       </c>
       <c r="F64" t="n">
-        <v>87.68170000000001</v>
+        <v>90.3977</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>52.6437</v>
+        <v>52.7349</v>
       </c>
       <c r="C65" t="n">
-        <v>100.434</v>
+        <v>100.963</v>
       </c>
       <c r="D65" t="n">
-        <v>379.735</v>
+        <v>376.859</v>
       </c>
       <c r="E65" t="n">
-        <v>52.3836</v>
+        <v>52.5822</v>
       </c>
       <c r="F65" t="n">
-        <v>88.9389</v>
+        <v>85.65470000000001</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>52.2247</v>
+        <v>52.2526</v>
       </c>
       <c r="C66" t="n">
-        <v>98.7355</v>
+        <v>97.9295</v>
       </c>
       <c r="D66" t="n">
-        <v>377.345</v>
+        <v>371.073</v>
       </c>
       <c r="E66" t="n">
-        <v>73.595</v>
+        <v>73.3398</v>
       </c>
       <c r="F66" t="n">
-        <v>158.039</v>
+        <v>158.009</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>70.7547</v>
+        <v>70.3476</v>
       </c>
       <c r="C67" t="n">
-        <v>174.405</v>
+        <v>172.72</v>
       </c>
       <c r="D67" t="n">
-        <v>360.257</v>
+        <v>356.783</v>
       </c>
       <c r="E67" t="n">
-        <v>71.3562</v>
+        <v>71.2868</v>
       </c>
       <c r="F67" t="n">
-        <v>153.431</v>
+        <v>154.352</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>68.6759</v>
+        <v>68.8248</v>
       </c>
       <c r="C68" t="n">
-        <v>167.007</v>
+        <v>167.526</v>
       </c>
       <c r="D68" t="n">
-        <v>358.62</v>
+        <v>353.738</v>
       </c>
       <c r="E68" t="n">
-        <v>69.46259999999999</v>
+        <v>69.6241</v>
       </c>
       <c r="F68" t="n">
-        <v>150.391</v>
+        <v>151.347</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>67.3639</v>
+        <v>67.209</v>
       </c>
       <c r="C69" t="n">
-        <v>166.632</v>
+        <v>166.179</v>
       </c>
       <c r="D69" t="n">
-        <v>342.485</v>
+        <v>343.292</v>
       </c>
       <c r="E69" t="n">
-        <v>67.4648</v>
+        <v>67.9044</v>
       </c>
       <c r="F69" t="n">
-        <v>146.905</v>
+        <v>147.127</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>65.4083</v>
+        <v>65.7932</v>
       </c>
       <c r="C70" t="n">
-        <v>157.107</v>
+        <v>162.974</v>
       </c>
       <c r="D70" t="n">
-        <v>335.061</v>
+        <v>337.876</v>
       </c>
       <c r="E70" t="n">
-        <v>66.08929999999999</v>
+        <v>66.1551</v>
       </c>
       <c r="F70" t="n">
-        <v>144.543</v>
+        <v>144.145</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>64.4834</v>
+        <v>64.324</v>
       </c>
       <c r="C71" t="n">
-        <v>156.03</v>
+        <v>156.35</v>
       </c>
       <c r="D71" t="n">
-        <v>336.178</v>
+        <v>338.564</v>
       </c>
       <c r="E71" t="n">
-        <v>64.71299999999999</v>
+        <v>64.5027</v>
       </c>
       <c r="F71" t="n">
-        <v>140.374</v>
+        <v>140.054</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>63.1747</v>
+        <v>63.2343</v>
       </c>
       <c r="C72" t="n">
-        <v>154.347</v>
+        <v>155.663</v>
       </c>
       <c r="D72" t="n">
-        <v>336.683</v>
+        <v>341.108</v>
       </c>
       <c r="E72" t="n">
-        <v>63.1207</v>
+        <v>62.9756</v>
       </c>
       <c r="F72" t="n">
-        <v>136.083</v>
+        <v>131.12</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>61.9683</v>
+        <v>61.8992</v>
       </c>
       <c r="C73" t="n">
-        <v>152.995</v>
+        <v>146.694</v>
       </c>
       <c r="D73" t="n">
-        <v>335.651</v>
+        <v>333.886</v>
       </c>
       <c r="E73" t="n">
-        <v>61.6425</v>
+        <v>61.7191</v>
       </c>
       <c r="F73" t="n">
-        <v>125.299</v>
+        <v>125.083</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>60.7928</v>
+        <v>60.6933</v>
       </c>
       <c r="C74" t="n">
-        <v>142.747</v>
+        <v>150.93</v>
       </c>
       <c r="D74" t="n">
-        <v>334.224</v>
+        <v>328.528</v>
       </c>
       <c r="E74" t="n">
-        <v>60.2557</v>
+        <v>60.1956</v>
       </c>
       <c r="F74" t="n">
-        <v>129.227</v>
+        <v>130.946</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>59.6687</v>
+        <v>59.3003</v>
       </c>
       <c r="C75" t="n">
-        <v>147.112</v>
+        <v>147.242</v>
       </c>
       <c r="D75" t="n">
-        <v>336.522</v>
+        <v>333.536</v>
       </c>
       <c r="E75" t="n">
-        <v>58.9167</v>
+        <v>59.1982</v>
       </c>
       <c r="F75" t="n">
-        <v>129.01</v>
+        <v>127.34</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>58.3184</v>
+        <v>58.5944</v>
       </c>
       <c r="C76" t="n">
-        <v>143.129</v>
+        <v>140.81</v>
       </c>
       <c r="D76" t="n">
-        <v>332.271</v>
+        <v>329.898</v>
       </c>
       <c r="E76" t="n">
-        <v>57.8554</v>
+        <v>57.6275</v>
       </c>
       <c r="F76" t="n">
-        <v>119.075</v>
+        <v>123.284</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>57.5685</v>
+        <v>57.7024</v>
       </c>
       <c r="C77" t="n">
-        <v>134.81</v>
+        <v>138.907</v>
       </c>
       <c r="D77" t="n">
-        <v>322.089</v>
+        <v>332.61</v>
       </c>
       <c r="E77" t="n">
-        <v>56.7986</v>
+        <v>56.9113</v>
       </c>
       <c r="F77" t="n">
-        <v>121.785</v>
+        <v>121.268</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>56.7273</v>
+        <v>56.6918</v>
       </c>
       <c r="C78" t="n">
-        <v>137.17</v>
+        <v>135.767</v>
       </c>
       <c r="D78" t="n">
-        <v>633.129</v>
+        <v>627.168</v>
       </c>
       <c r="E78" t="n">
-        <v>56.4411</v>
+        <v>55.9981</v>
       </c>
       <c r="F78" t="n">
-        <v>118.946</v>
+        <v>112.617</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>56.0905</v>
+        <v>55.7809</v>
       </c>
       <c r="C79" t="n">
-        <v>133.491</v>
+        <v>134.652</v>
       </c>
       <c r="D79" t="n">
-        <v>604.97</v>
+        <v>607.3869999999999</v>
       </c>
       <c r="E79" t="n">
-        <v>55.8135</v>
+        <v>55.715</v>
       </c>
       <c r="F79" t="n">
-        <v>118.113</v>
+        <v>119.835</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>55.4518</v>
+        <v>56.1109</v>
       </c>
       <c r="C80" t="n">
-        <v>132.855</v>
+        <v>133.645</v>
       </c>
       <c r="D80" t="n">
-        <v>579.758</v>
+        <v>602.534</v>
       </c>
       <c r="E80" t="n">
-        <v>79.4815</v>
+        <v>81.34399999999999</v>
       </c>
       <c r="F80" t="n">
-        <v>211.988</v>
+        <v>216.565</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>75.3049</v>
+        <v>75.79859999999999</v>
       </c>
       <c r="C81" t="n">
-        <v>244.479</v>
+        <v>246.161</v>
       </c>
       <c r="D81" t="n">
-        <v>585.996</v>
+        <v>605.403</v>
       </c>
       <c r="E81" t="n">
-        <v>77.28270000000001</v>
+        <v>78.1062</v>
       </c>
       <c r="F81" t="n">
-        <v>223.939</v>
+        <v>228.998</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>74.5517</v>
+        <v>75.36320000000001</v>
       </c>
       <c r="C82" t="n">
-        <v>246.521</v>
+        <v>247.722</v>
       </c>
       <c r="D82" t="n">
-        <v>555.494</v>
+        <v>539.205</v>
       </c>
       <c r="E82" t="n">
-        <v>77.4246</v>
+        <v>77.1309</v>
       </c>
       <c r="F82" t="n">
-        <v>226.587</v>
+        <v>218.398</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>76.7456</v>
+        <v>75.5855</v>
       </c>
       <c r="C83" t="n">
-        <v>243.981</v>
+        <v>241.482</v>
       </c>
       <c r="D83" t="n">
-        <v>537.081</v>
+        <v>554.4109999999999</v>
       </c>
       <c r="E83" t="n">
-        <v>75.8417</v>
+        <v>76.38720000000001</v>
       </c>
       <c r="F83" t="n">
-        <v>201.273</v>
+        <v>216.38</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>75.8163</v>
+        <v>75.4751</v>
       </c>
       <c r="C84" t="n">
-        <v>238.938</v>
+        <v>236.675</v>
       </c>
       <c r="D84" t="n">
-        <v>544.976</v>
+        <v>551.7670000000001</v>
       </c>
       <c r="E84" t="n">
-        <v>75.131</v>
+        <v>75.482</v>
       </c>
       <c r="F84" t="n">
-        <v>213.742</v>
+        <v>201.312</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>75.5716</v>
+        <v>75.49339999999999</v>
       </c>
       <c r="C85" t="n">
-        <v>233.641</v>
+        <v>223.806</v>
       </c>
       <c r="D85" t="n">
-        <v>544.448</v>
+        <v>511.172</v>
       </c>
       <c r="E85" t="n">
-        <v>73.70910000000001</v>
+        <v>74.1194</v>
       </c>
       <c r="F85" t="n">
-        <v>198.34</v>
+        <v>206.476</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>75.78740000000001</v>
+        <v>75.64870000000001</v>
       </c>
       <c r="C86" t="n">
-        <v>227.524</v>
+        <v>227.296</v>
       </c>
       <c r="D86" t="n">
-        <v>510.983</v>
+        <v>540.534</v>
       </c>
       <c r="E86" t="n">
-        <v>72.65819999999999</v>
+        <v>72.48869999999999</v>
       </c>
       <c r="F86" t="n">
-        <v>200.152</v>
+        <v>194.579</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>75.19629999999999</v>
+        <v>74.8152</v>
       </c>
       <c r="C87" t="n">
-        <v>218.841</v>
+        <v>220.394</v>
       </c>
       <c r="D87" t="n">
-        <v>524.422</v>
+        <v>515.287</v>
       </c>
       <c r="E87" t="n">
-        <v>71.3991</v>
+        <v>71.29130000000001</v>
       </c>
       <c r="F87" t="n">
-        <v>176.79</v>
+        <v>184.338</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>74.4149</v>
+        <v>74.90479999999999</v>
       </c>
       <c r="C88" t="n">
-        <v>215.862</v>
+        <v>216.701</v>
       </c>
       <c r="D88" t="n">
-        <v>511.942</v>
+        <v>519.391</v>
       </c>
       <c r="E88" t="n">
-        <v>69.6906</v>
+        <v>70.13630000000001</v>
       </c>
       <c r="F88" t="n">
-        <v>186.629</v>
+        <v>188.753</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>73.38630000000001</v>
+        <v>73.8608</v>
       </c>
       <c r="C89" t="n">
-        <v>211.229</v>
+        <v>210.218</v>
       </c>
       <c r="D89" t="n">
-        <v>521.006</v>
+        <v>514.937</v>
       </c>
       <c r="E89" t="n">
-        <v>67.9559</v>
+        <v>68.50620000000001</v>
       </c>
       <c r="F89" t="n">
-        <v>186.935</v>
+        <v>187.95</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>73.0932</v>
+        <v>73.28279999999999</v>
       </c>
       <c r="C90" t="n">
-        <v>207.985</v>
+        <v>209.534</v>
       </c>
       <c r="D90" t="n">
-        <v>499.213</v>
+        <v>503.658</v>
       </c>
       <c r="E90" t="n">
-        <v>67.2058</v>
+        <v>67.5184</v>
       </c>
       <c r="F90" t="n">
-        <v>185.017</v>
+        <v>179.685</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>73.2059</v>
+        <v>73.3232</v>
       </c>
       <c r="C91" t="n">
-        <v>204.668</v>
+        <v>204.818</v>
       </c>
       <c r="D91" t="n">
-        <v>493.446</v>
+        <v>500.315</v>
       </c>
       <c r="E91" t="n">
-        <v>66.675</v>
+        <v>66.8009</v>
       </c>
       <c r="F91" t="n">
-        <v>174.609</v>
+        <v>177.382</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>72.7462</v>
+        <v>72.68470000000001</v>
       </c>
       <c r="C92" t="n">
-        <v>198.251</v>
+        <v>199.706</v>
       </c>
       <c r="D92" t="n">
-        <v>822.404</v>
+        <v>834.212</v>
       </c>
       <c r="E92" t="n">
-        <v>64.95780000000001</v>
+        <v>65.3707</v>
       </c>
       <c r="F92" t="n">
-        <v>179.141</v>
+        <v>178.247</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>72.73860000000001</v>
+        <v>73.004</v>
       </c>
       <c r="C93" t="n">
-        <v>194.96</v>
+        <v>196.874</v>
       </c>
       <c r="D93" t="n">
-        <v>827.191</v>
+        <v>825.692</v>
       </c>
       <c r="E93" t="n">
-        <v>63.7704</v>
+        <v>64.78579999999999</v>
       </c>
       <c r="F93" t="n">
-        <v>170.897</v>
+        <v>172.755</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>71.75</v>
+        <v>72.2351</v>
       </c>
       <c r="C94" t="n">
-        <v>192.506</v>
+        <v>190.313</v>
       </c>
       <c r="D94" t="n">
-        <v>773.228</v>
+        <v>773.327</v>
       </c>
       <c r="E94" t="n">
-        <v>96.7128</v>
+        <v>97.4301</v>
       </c>
       <c r="F94" t="n">
-        <v>326.623</v>
+        <v>326.462</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>91.3036</v>
+        <v>94.1395</v>
       </c>
       <c r="C95" t="n">
-        <v>362.776</v>
+        <v>362.223</v>
       </c>
       <c r="D95" t="n">
-        <v>784.832</v>
+        <v>784.451</v>
       </c>
       <c r="E95" t="n">
-        <v>95.3356</v>
+        <v>95.0663</v>
       </c>
       <c r="F95" t="n">
-        <v>305.15</v>
+        <v>300.138</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>91.2704</v>
+        <v>92.53740000000001</v>
       </c>
       <c r="C96" t="n">
-        <v>345.153</v>
+        <v>348.819</v>
       </c>
       <c r="D96" t="n">
-        <v>733.706</v>
+        <v>738.153</v>
       </c>
       <c r="E96" t="n">
-        <v>90.7</v>
+        <v>92.3387</v>
       </c>
       <c r="F96" t="n">
-        <v>290.849</v>
+        <v>286.102</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>92.82940000000001</v>
+        <v>93.1927</v>
       </c>
       <c r="C97" t="n">
-        <v>329.718</v>
+        <v>343.706</v>
       </c>
       <c r="D97" t="n">
-        <v>741.968</v>
+        <v>742.34</v>
       </c>
       <c r="E97" t="n">
-        <v>90.06619999999999</v>
+        <v>89.98739999999999</v>
       </c>
       <c r="F97" t="n">
-        <v>293.722</v>
+        <v>285.024</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>94.9481</v>
+        <v>95.2277</v>
       </c>
       <c r="C98" t="n">
-        <v>337.069</v>
+        <v>334.663</v>
       </c>
       <c r="D98" t="n">
-        <v>723.9400000000001</v>
+        <v>725.026</v>
       </c>
       <c r="E98" t="n">
-        <v>90.6375</v>
+        <v>91.87350000000001</v>
       </c>
       <c r="F98" t="n">
-        <v>283.488</v>
+        <v>282.735</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>94.40779999999999</v>
+        <v>93.16289999999999</v>
       </c>
       <c r="C99" t="n">
-        <v>314.933</v>
+        <v>321.324</v>
       </c>
       <c r="D99" t="n">
-        <v>706.4349999999999</v>
+        <v>700.8630000000001</v>
       </c>
       <c r="E99" t="n">
-        <v>88.6242</v>
+        <v>92.2444</v>
       </c>
       <c r="F99" t="n">
-        <v>263.007</v>
+        <v>270.268</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>93.535</v>
+        <v>94.0313</v>
       </c>
       <c r="C100" t="n">
-        <v>314.283</v>
+        <v>302.01</v>
       </c>
       <c r="D100" t="n">
-        <v>690.802</v>
+        <v>693.37</v>
       </c>
       <c r="E100" t="n">
-        <v>91.63760000000001</v>
+        <v>92.93380000000001</v>
       </c>
       <c r="F100" t="n">
-        <v>283.029</v>
+        <v>269.102</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>96.301</v>
+        <v>95.6647</v>
       </c>
       <c r="C101" t="n">
-        <v>321.945</v>
+        <v>323.358</v>
       </c>
       <c r="D101" t="n">
-        <v>677.6319999999999</v>
+        <v>682.753</v>
       </c>
       <c r="E101" t="n">
-        <v>87.98480000000001</v>
+        <v>89.36320000000001</v>
       </c>
       <c r="F101" t="n">
-        <v>283.73</v>
+        <v>277.105</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>97.26139999999999</v>
+        <v>96.6305</v>
       </c>
       <c r="C102" t="n">
-        <v>315.033</v>
+        <v>302.072</v>
       </c>
       <c r="D102" t="n">
-        <v>666.763</v>
+        <v>657.5839999999999</v>
       </c>
       <c r="E102" t="n">
-        <v>88.5433</v>
+        <v>86.6511</v>
       </c>
       <c r="F102" t="n">
-        <v>280.64</v>
+        <v>268.418</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>97.4953</v>
+        <v>95.87949999999999</v>
       </c>
       <c r="C103" t="n">
-        <v>312.435</v>
+        <v>305.544</v>
       </c>
       <c r="D103" t="n">
-        <v>655.678</v>
+        <v>645.069</v>
       </c>
       <c r="E103" t="n">
-        <v>89.357</v>
+        <v>88.8998</v>
       </c>
       <c r="F103" t="n">
-        <v>276.845</v>
+        <v>261.341</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>97.5234</v>
+        <v>95.1343</v>
       </c>
       <c r="C104" t="n">
-        <v>308.086</v>
+        <v>286.582</v>
       </c>
       <c r="D104" t="n">
-        <v>648.772</v>
+        <v>638.17</v>
       </c>
       <c r="E104" t="n">
-        <v>86.795</v>
+        <v>85.7817</v>
       </c>
       <c r="F104" t="n">
-        <v>266.888</v>
+        <v>257.724</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>98.011</v>
+        <v>96.0667</v>
       </c>
       <c r="C105" t="n">
-        <v>305.817</v>
+        <v>274.206</v>
       </c>
       <c r="D105" t="n">
-        <v>648.957</v>
+        <v>633.616</v>
       </c>
       <c r="E105" t="n">
-        <v>86.3278</v>
+        <v>85.47620000000001</v>
       </c>
       <c r="F105" t="n">
-        <v>251.425</v>
+        <v>254.18</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>97.8621</v>
+        <v>95.99209999999999</v>
       </c>
       <c r="C106" t="n">
-        <v>294.415</v>
+        <v>285.855</v>
       </c>
       <c r="D106" t="n">
-        <v>640.051</v>
+        <v>625.4059999999999</v>
       </c>
       <c r="E106" t="n">
-        <v>84.4992</v>
+        <v>86.0796</v>
       </c>
       <c r="F106" t="n">
-        <v>243.257</v>
+        <v>254.661</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>99.07510000000001</v>
+        <v>98.2393</v>
       </c>
       <c r="C107" t="n">
-        <v>284.368</v>
+        <v>285.202</v>
       </c>
       <c r="D107" t="n">
-        <v>948.856</v>
+        <v>945.758</v>
       </c>
       <c r="E107" t="n">
-        <v>86.2368</v>
+        <v>86.5232</v>
       </c>
       <c r="F107" t="n">
-        <v>252.955</v>
+        <v>250.848</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>99.2903</v>
+        <v>100.142</v>
       </c>
       <c r="C108" t="n">
-        <v>279.09</v>
+        <v>269.113</v>
       </c>
       <c r="D108" t="n">
-        <v>920.2569999999999</v>
+        <v>921.851</v>
       </c>
       <c r="E108" t="n">
-        <v>131.644</v>
+        <v>129.736</v>
       </c>
       <c r="F108" t="n">
-        <v>405.79</v>
+        <v>431.292</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>104.534</v>
+        <v>106.917</v>
       </c>
       <c r="C109" t="n">
-        <v>259.289</v>
+        <v>267.223</v>
       </c>
       <c r="D109" t="n">
-        <v>883.199</v>
+        <v>905.316</v>
       </c>
       <c r="E109" t="n">
-        <v>110.784</v>
+        <v>115.814</v>
       </c>
       <c r="F109" t="n">
-        <v>414.829</v>
+        <v>407.953</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>145.822</v>
+        <v>146.11</v>
       </c>
       <c r="C110" t="n">
-        <v>429.874</v>
+        <v>437.94</v>
       </c>
       <c r="D110" t="n">
-        <v>874.326</v>
+        <v>870.957</v>
       </c>
       <c r="E110" t="n">
-        <v>135.912</v>
+        <v>135.887</v>
       </c>
       <c r="F110" t="n">
-        <v>403.514</v>
+        <v>401.755</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>145.53</v>
+        <v>145.556</v>
       </c>
       <c r="C111" t="n">
-        <v>419.983</v>
+        <v>425.32</v>
       </c>
       <c r="D111" t="n">
-        <v>849.875</v>
+        <v>849.151</v>
       </c>
       <c r="E111" t="n">
-        <v>126.193</v>
+        <v>121.163</v>
       </c>
       <c r="F111" t="n">
-        <v>387.856</v>
+        <v>393.452</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>132.42</v>
+        <v>133.212</v>
       </c>
       <c r="C112" t="n">
-        <v>413.462</v>
+        <v>418.099</v>
       </c>
       <c r="D112" t="n">
-        <v>824.83</v>
+        <v>823.1130000000001</v>
       </c>
       <c r="E112" t="n">
-        <v>109.463</v>
+        <v>114.045</v>
       </c>
       <c r="F112" t="n">
-        <v>394.453</v>
+        <v>377.311</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>120.873</v>
+        <v>118.953</v>
       </c>
       <c r="C113" t="n">
-        <v>420.324</v>
+        <v>412.271</v>
       </c>
       <c r="D113" t="n">
-        <v>829.837</v>
+        <v>805.558</v>
       </c>
       <c r="E113" t="n">
-        <v>111.575</v>
+        <v>114.487</v>
       </c>
       <c r="F113" t="n">
-        <v>394.391</v>
+        <v>382.834</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>120.933</v>
+        <v>118.225</v>
       </c>
       <c r="C114" t="n">
-        <v>416.752</v>
+        <v>409.754</v>
       </c>
       <c r="D114" t="n">
-        <v>820.755</v>
+        <v>799.437</v>
       </c>
       <c r="E114" t="n">
-        <v>111.521</v>
+        <v>116.642</v>
       </c>
       <c r="F114" t="n">
-        <v>374.478</v>
+        <v>377.96</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>123.756</v>
+        <v>124.762</v>
       </c>
       <c r="C115" t="n">
-        <v>401.304</v>
+        <v>392.981</v>
       </c>
       <c r="D115" t="n">
-        <v>801.424</v>
+        <v>800.466</v>
       </c>
       <c r="E115" t="n">
-        <v>111.627</v>
+        <v>111.14</v>
       </c>
       <c r="F115" t="n">
-        <v>368.021</v>
+        <v>366.803</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>130.23</v>
+        <v>138.468</v>
       </c>
       <c r="C116" t="n">
-        <v>397.092</v>
+        <v>392.342</v>
       </c>
       <c r="D116" t="n">
-        <v>773.022</v>
+        <v>790.901</v>
       </c>
       <c r="E116" t="n">
-        <v>110.943</v>
+        <v>112.948</v>
       </c>
       <c r="F116" t="n">
-        <v>356.363</v>
+        <v>366.403</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>133.389</v>
+        <v>137.692</v>
       </c>
       <c r="C117" t="n">
-        <v>368.515</v>
+        <v>378.776</v>
       </c>
       <c r="D117" t="n">
-        <v>770.924</v>
+        <v>793.252</v>
       </c>
       <c r="E117" t="n">
-        <v>114.693</v>
+        <v>118.698</v>
       </c>
       <c r="F117" t="n">
-        <v>340.631</v>
+        <v>356.955</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>127.757</v>
+        <v>130.178</v>
       </c>
       <c r="C118" t="n">
-        <v>358.36</v>
+        <v>369.604</v>
       </c>
       <c r="D118" t="n">
-        <v>750.99</v>
+        <v>767.5069999999999</v>
       </c>
       <c r="E118" t="n">
-        <v>110.636</v>
+        <v>117.673</v>
       </c>
       <c r="F118" t="n">
-        <v>326.256</v>
+        <v>337.686</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>134.174</v>
+        <v>141.991</v>
       </c>
       <c r="C119" t="n">
-        <v>344.272</v>
+        <v>356.211</v>
       </c>
       <c r="D119" t="n">
-        <v>740.463</v>
+        <v>756.588</v>
       </c>
       <c r="E119" t="n">
-        <v>116.989</v>
+        <v>120.98</v>
       </c>
       <c r="F119" t="n">
-        <v>320.304</v>
+        <v>326.974</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>135.889</v>
+        <v>140.068</v>
       </c>
       <c r="C120" t="n">
-        <v>344.316</v>
+        <v>347.582</v>
       </c>
       <c r="D120" t="n">
-        <v>739.275</v>
+        <v>746.389</v>
       </c>
       <c r="E120" t="n">
-        <v>124.199</v>
+        <v>124.807</v>
       </c>
       <c r="F120" t="n">
-        <v>319.712</v>
+        <v>320.178</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>141.302</v>
+        <v>141.575</v>
       </c>
       <c r="C121" t="n">
-        <v>352.078</v>
+        <v>347.496</v>
       </c>
       <c r="D121" t="n">
-        <v>1067.42</v>
+        <v>1063.12</v>
       </c>
       <c r="E121" t="n">
-        <v>128.323</v>
+        <v>124.703</v>
       </c>
       <c r="F121" t="n">
-        <v>315.438</v>
+        <v>314.733</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>141.669</v>
+        <v>142.243</v>
       </c>
       <c r="C122" t="n">
-        <v>338.743</v>
+        <v>338.432</v>
       </c>
       <c r="D122" t="n">
-        <v>1061.1</v>
+        <v>1059.62</v>
       </c>
       <c r="E122" t="n">
-        <v>128.388</v>
+        <v>127.299</v>
       </c>
       <c r="F122" t="n">
-        <v>306.418</v>
+        <v>315.921</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>138.927</v>
+        <v>141.48</v>
       </c>
       <c r="C123" t="n">
-        <v>334.528</v>
+        <v>335.13</v>
       </c>
       <c r="D123" t="n">
-        <v>1037.01</v>
+        <v>1034.03</v>
       </c>
       <c r="E123" t="n">
-        <v>167.16</v>
+        <v>165.756</v>
       </c>
       <c r="F123" t="n">
-        <v>468.798</v>
+        <v>486.499</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>171.939</v>
+        <v>178.364</v>
       </c>
       <c r="C124" t="n">
-        <v>491.391</v>
+        <v>513.71</v>
       </c>
       <c r="D124" t="n">
-        <v>980.327</v>
+        <v>983.4450000000001</v>
       </c>
       <c r="E124" t="n">
-        <v>165.507</v>
+        <v>168.81</v>
       </c>
       <c r="F124" t="n">
-        <v>449.206</v>
+        <v>472.96</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>169.487</v>
+        <v>174.711</v>
       </c>
       <c r="C125" t="n">
-        <v>478.184</v>
+        <v>496.627</v>
       </c>
       <c r="D125" t="n">
-        <v>957.977</v>
+        <v>973.592</v>
       </c>
       <c r="E125" t="n">
-        <v>162.921</v>
+        <v>163.032</v>
       </c>
       <c r="F125" t="n">
-        <v>444.175</v>
+        <v>459.878</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>175.318</v>
+        <v>172.584</v>
       </c>
       <c r="C126" t="n">
-        <v>464.567</v>
+        <v>481.406</v>
       </c>
       <c r="D126" t="n">
-        <v>925.3099999999999</v>
+        <v>947.813</v>
       </c>
       <c r="E126" t="n">
-        <v>163.987</v>
+        <v>169.424</v>
       </c>
       <c r="F126" t="n">
-        <v>436.013</v>
+        <v>448.748</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>176.667</v>
+        <v>175.948</v>
       </c>
       <c r="C127" t="n">
-        <v>460.878</v>
+        <v>468.503</v>
       </c>
       <c r="D127" t="n">
-        <v>909.2809999999999</v>
+        <v>924.296</v>
       </c>
       <c r="E127" t="n">
-        <v>166.578</v>
+        <v>165.864</v>
       </c>
       <c r="F127" t="n">
-        <v>425.225</v>
+        <v>436.218</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>176.46</v>
+        <v>178.54</v>
       </c>
       <c r="C128" t="n">
-        <v>468.211</v>
+        <v>485.044</v>
       </c>
       <c r="D128" t="n">
-        <v>905.457</v>
+        <v>925.6319999999999</v>
       </c>
       <c r="E128" t="n">
-        <v>167.627</v>
+        <v>168.013</v>
       </c>
       <c r="F128" t="n">
-        <v>435.862</v>
+        <v>452.217</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>175.435</v>
+        <v>178.955</v>
       </c>
       <c r="C129" t="n">
-        <v>457.03</v>
+        <v>474.508</v>
       </c>
       <c r="D129" t="n">
-        <v>880.011</v>
+        <v>899.2</v>
       </c>
       <c r="E129" t="n">
-        <v>164.842</v>
+        <v>171.097</v>
       </c>
       <c r="F129" t="n">
-        <v>424.26</v>
+        <v>438.884</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>175.582</v>
+        <v>179.219</v>
       </c>
       <c r="C130" t="n">
-        <v>446.557</v>
+        <v>461.284</v>
       </c>
       <c r="D130" t="n">
-        <v>856.965</v>
+        <v>873.107</v>
       </c>
       <c r="E130" t="n">
-        <v>170.25</v>
+        <v>170.414</v>
       </c>
       <c r="F130" t="n">
-        <v>430.134</v>
+        <v>431.12</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>178.958</v>
+        <v>177.767</v>
       </c>
       <c r="C131" t="n">
-        <v>451.95</v>
+        <v>451.972</v>
       </c>
       <c r="D131" t="n">
-        <v>857.982</v>
+        <v>858.17</v>
       </c>
       <c r="E131" t="n">
-        <v>168.982</v>
+        <v>169.12</v>
       </c>
       <c r="F131" t="n">
-        <v>416.894</v>
+        <v>418.787</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>179.107</v>
+        <v>176.367</v>
       </c>
       <c r="C132" t="n">
-        <v>434.46</v>
+        <v>440.931</v>
       </c>
       <c r="D132" t="n">
-        <v>841.148</v>
+        <v>859.823</v>
       </c>
       <c r="E132" t="n">
-        <v>163.615</v>
+        <v>166.771</v>
       </c>
       <c r="F132" t="n">
-        <v>394.396</v>
+        <v>404.105</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>173.191</v>
+        <v>176.708</v>
       </c>
       <c r="C133" t="n">
-        <v>419.144</v>
+        <v>419.885</v>
       </c>
       <c r="D133" t="n">
-        <v>825.29</v>
+        <v>824.083</v>
       </c>
       <c r="E133" t="n">
-        <v>162.347</v>
+        <v>162.7</v>
       </c>
       <c r="F133" t="n">
-        <v>390.766</v>
+        <v>393.735</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>170.748</v>
+        <v>176.862</v>
       </c>
       <c r="C134" t="n">
-        <v>412.389</v>
+        <v>420.016</v>
       </c>
       <c r="D134" t="n">
-        <v>810.617</v>
+        <v>818.8049999999999</v>
       </c>
       <c r="E134" t="n">
-        <v>161.505</v>
+        <v>166.394</v>
       </c>
       <c r="F134" t="n">
-        <v>385.752</v>
+        <v>387.853</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>175.479</v>
+        <v>176.449</v>
       </c>
       <c r="C135" t="n">
-        <v>404.261</v>
+        <v>413.484</v>
       </c>
       <c r="D135" t="n">
-        <v>1119.27</v>
+        <v>1150.06</v>
       </c>
       <c r="E135" t="n">
-        <v>160.508</v>
+        <v>165.788</v>
       </c>
       <c r="F135" t="n">
-        <v>376.678</v>
+        <v>385.359</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>170.937</v>
+        <v>175.84</v>
       </c>
       <c r="C136" t="n">
-        <v>400.538</v>
+        <v>406.397</v>
       </c>
       <c r="D136" t="n">
-        <v>1137.43</v>
+        <v>1137.53</v>
       </c>
       <c r="E136" t="n">
-        <v>165.869</v>
+        <v>165.125</v>
       </c>
       <c r="F136" t="n">
-        <v>381.517</v>
+        <v>378.122</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>175.901</v>
+        <v>174.39</v>
       </c>
       <c r="C137" t="n">
-        <v>400.236</v>
+        <v>396.677</v>
       </c>
       <c r="D137" t="n">
-        <v>1082.51</v>
+        <v>1056.39</v>
       </c>
       <c r="E137" t="n">
-        <v>207.93</v>
+        <v>202.191</v>
       </c>
       <c r="F137" t="n">
-        <v>562.572</v>
+        <v>554.0700000000001</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>212.645</v>
+        <v>206.485</v>
       </c>
       <c r="C138" t="n">
-        <v>597.152</v>
+        <v>586.987</v>
       </c>
       <c r="D138" t="n">
-        <v>1078.42</v>
+        <v>1052.42</v>
       </c>
       <c r="E138" t="n">
-        <v>207.483</v>
+        <v>206.116</v>
       </c>
       <c r="F138" t="n">
-        <v>546.388</v>
+        <v>532.6660000000001</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>212.604</v>
+        <v>205.652</v>
       </c>
       <c r="C139" t="n">
-        <v>578.093</v>
+        <v>565.013</v>
       </c>
       <c r="D139" t="n">
-        <v>1062.04</v>
+        <v>1031.23</v>
       </c>
       <c r="E139" t="n">
-        <v>203.311</v>
+        <v>198.145</v>
       </c>
       <c r="F139" t="n">
-        <v>532.018</v>
+        <v>513.386</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>210.126</v>
+        <v>203.709</v>
       </c>
       <c r="C140" t="n">
-        <v>557.028</v>
+        <v>545.1849999999999</v>
       </c>
       <c r="D140" t="n">
-        <v>1004.22</v>
+        <v>997.907</v>
       </c>
       <c r="E140" t="n">
-        <v>197.567</v>
+        <v>196.245</v>
       </c>
       <c r="F140" t="n">
-        <v>508.972</v>
+        <v>500.744</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>203.218</v>
+        <v>202.208</v>
       </c>
       <c r="C141" t="n">
-        <v>535.157</v>
+        <v>532.231</v>
       </c>
       <c r="D141" t="n">
-        <v>988.449</v>
+        <v>979.928</v>
       </c>
       <c r="E141" t="n">
-        <v>195.675</v>
+        <v>194.397</v>
       </c>
       <c r="F141" t="n">
-        <v>496.584</v>
+        <v>491.374</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>201.344</v>
+        <v>199.734</v>
       </c>
       <c r="C142" t="n">
-        <v>527.324</v>
+        <v>526.255</v>
       </c>
       <c r="D142" t="n">
-        <v>965.428</v>
+        <v>957.196</v>
       </c>
       <c r="E142" t="n">
-        <v>193.797</v>
+        <v>193.1</v>
       </c>
       <c r="F142" t="n">
-        <v>489.215</v>
+        <v>480.942</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>204.369</v>
+        <v>198.775</v>
       </c>
       <c r="C143" t="n">
-        <v>518.773</v>
+        <v>503.484</v>
       </c>
       <c r="D143" t="n">
-        <v>959.448</v>
+        <v>945.51</v>
       </c>
       <c r="E143" t="n">
-        <v>196.474</v>
+        <v>198.001</v>
       </c>
       <c r="F143" t="n">
-        <v>477.305</v>
+        <v>479.125</v>
       </c>
     </row>
   </sheetData>
